--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -8,8 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experience" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testimonials" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000284C7"/>
+        <fgColor rgb="007C5CE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,8 +61,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -428,11 +432,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,102 +451,1206 @@
           <t>value</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note (what this changes)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tagline</t>
+          <t>logo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>I am learning</t>
+          <t>Mohd Saud</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Name in the top-left of the menu</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>lead</t>
+          <t>greeting</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Computer Science graduate with 4+ years of customer-facing operations experience, now building hands-on skills in AWS, Terraform, Docker, CI/CD and Cloud Security.</t>
+          <t>Hello, I'm</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Small purple text above your name</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>about1</t>
+          <t>name_line1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>I started my career as a Service Advisor at Oneup Motors (Maruti Suzuki dealership, Lucknow), handling customers, technicians, escalations and billing in a high-volume workshop. That taught me responsibility, communication and problem-solving under pressure.</t>
+          <t>Mohd</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Big name, line 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>about2</t>
+          <t>name_line2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>I then completed my B.Tech in Computer Science (AKTU, 2026) and moved into technology. My focus is Cloud and DevOps, with Cloud Security as my longer-term direction. I learn by building, breaking things, and documenting what I fix.</t>
+          <t>Saud</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Big name, line 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>hero_split</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>mosaud1997@icloud.com</t>
+          <t>Aspiring</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Small word above the animated title</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>hero_profession1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohdsaud1</t>
+          <t>Cloud DevOps</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Animated purple line</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hero_profession2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Iamsaudkhan</t>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Animated white line</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>open_to</t>
+          <t>about_title_highlight</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Open to internships and entry-level Cloud / DevOps opportunities.</t>
-        </is>
-      </c>
+          <t>Discipline</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Purple part of the About title</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>about_title_rest</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Builds Freedom</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>White part of the About title</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>about_text</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>I'm a **Cloud &amp; DevOps** engineer in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Wrap words in **double stars** to make them purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>contact_text</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Open to internships and entry-level Cloud / DevOps roles. Let's talk!</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Line above the Copy email button</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>mosaud1997@icloud.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Shown in Contact + used by Copy email</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Lucknow, Uttar Pradesh, India</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Shown in Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohdsaud1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Full https:// link</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Iamsaudkhan</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Full https:// link</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Path or link to your resume PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -554,13 +1663,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,37 +1683,59 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>items (separate with ;)</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>level (Learning / Hands-on / Strong)</t>
+          <t>stack (comma separated)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>visible (yes/no)</t>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>visible</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>DevSecOps</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AWS (EC2, S3, VPC, IAM, ECR, Route 53, Secrets Manager, CloudWatch); GCP</t>
+          <t>Secure Cloud DevSecOps Pipeline</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>AWS, Terraform, GitHub Actions, Docker, Trivy, ECR, EC2, CloudWatch</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -610,20 +1744,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DevOps &amp; IaC</t>
+          <t>IaC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Terraform; Docker; GitHub Actions; CI/CD; Trivy</t>
+          <t>AWS Infrastructure as Code</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>AWS, Terraform, S3, DynamoDB, IAM, VPC</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -632,70 +1773,1809 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Linux &amp; Networking</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ubuntu; Bash; TCP/IP; DNS; VPC subnetting; Security Groups</t>
+          <t>Personal Portfolio Website</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>HTML, CSS, JavaScript, GitHub Pages, Google Sheets</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/MOHDSAUD888/Mohd-Saud_Portfolio-Website</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Programming &amp; Tools</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Python; HTML/CSS/JS; Git; GitHub; MySQL</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Professional</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Communication; Customer handling; Coordination; Working under pressure</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+      <c r="G141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="n"/>
+      <c r="G147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="n"/>
+      <c r="G151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="n"/>
+      <c r="G157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="n"/>
+      <c r="G163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="n"/>
+      <c r="G167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="2" t="n"/>
+      <c r="G171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="n"/>
+      <c r="G173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="n"/>
+      <c r="G174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
+      <c r="G179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="n"/>
+      <c r="G185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="2" t="n"/>
+      <c r="G187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="n"/>
+      <c r="G189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="n"/>
+      <c r="G192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="2" t="n"/>
+      <c r="G193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="n"/>
+      <c r="G195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n"/>
+      <c r="G197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+      <c r="G199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="2" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"In progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -706,90 +3586,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>stack (separate with ;)</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>learned</t>
+          <t>period</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>status (In progress / Completed)</t>
+          <t>description</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>repo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>visible (yes/no)</t>
+          <t>visible</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>End-to-End Secure Cloud DevSecOps Pipeline &amp; AWS Infrastructure</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Automate testing, security scanning and deployment of a containerized app on AWS.</t>
+          <t>Service Advisor</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AWS; Terraform; GitHub Actions; Docker; Trivy; ECR; EC2; CloudWatch</t>
+          <t>Oneup Motors India Pvt. Ltd. (Maruti Suzuki)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Shift-left security with Trivy, custom VPC with Terraform, least-privilege IAM and Secrets Manager.</t>
+          <t>Sep 2019 – May 2023</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+          <t>Managed customer service in a high-volume automotive workshop: coordinated with technicians, handled client communication and escalations, and managed service documentation and billing.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -798,32 +3664,30 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Automated AWS Infrastructure as Code (IaC) Provisioning</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Make multi-tier AWS environments repeatable and safe for team use.</t>
+          <t>B.Tech, Computer Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>AWS; Terraform; IaC; Cloud Security; GitHub</t>
+          <t>Dr. A.P.J. Abdul Kalam Technical University (AKTU), Lucknow</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Modular Terraform, remote state with DynamoDB locking, zero-trust Security Groups, encrypted S3.</t>
+          <t>Graduated 2026</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+          <t>Studied computer science fundamentals, programming, networking and problem solving, and moved into Cloud and DevOps through hands-on projects.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -832,42 +3696,4816 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>This Portfolio Website</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Present my skills and learning journey clearly, and update it from a Google Sheet.</t>
+          <t>AWS Solutions Architect – Associate</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HTML; CSS; JavaScript; GitHub Pages; Google Sheets</t>
+          <t>Certification (in progress) · GCP Skills Boost labs</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Responsive layout, CSS variables for theming, fetching CSV data, deployment.</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Preparing for AWS SAA and practising on Google Cloud Skills Boost labs to strengthen cloud architecture skills.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/MOHDSAUD888/Mohd-Saud_Portfolio-Website</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>yes</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Diploma, Automobile Engineering</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Integral University, Lucknow</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Built a strong technical base in automobile systems, which led to my first professional role in the automotive industry.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+      <c r="F160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Experience,Education"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>items (comma separated)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cloud &amp; DevOps</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Building, automating and deploying infrastructure on AWS with Infrastructure as Code and CI/CD.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>AWS EC2, S3, VPC, IAM, ECR, Route 53, Secrets Manager, CloudWatch, GCP, Terraform, Docker, GitHub Actions, CI/CD, Trivy</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Linux &amp; Networking</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Solid foundation in Linux administration, networking and cloud security basics.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Ubuntu, Bash Scripting, Linux Administration, TCP/IP, DNS, DHCP, HTTP/HTTPS, VPC Subnetting, Routing Tables, Firewalls, Security Groups</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tools &amp; Languages</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tools and languages I use every day to build, test and document my work.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Python, HTML, CSS, JavaScript, Git, GitHub, VS Code, MySQL, VMware, VirtualBox, Kali Linux, Windows Server</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Professional Skills</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Strengths from nearly four years of real customer-facing work in the automobile industry.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Handling, Escalation Management, Team Coordination, Documentation, Billing, Communication, Working Under Pressure</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
+      <c r="F111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="n"/>
+      <c r="F160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="n"/>
+      <c r="F187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
+      <c r="F193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Experience" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Testimonials" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,14 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007C5CE0"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -67,6 +76,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,9 +446,9 @@
   <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +481,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Name in the top-left of the menu</t>
+          <t>Name in the menu and the footer</t>
         </is>
       </c>
     </row>
@@ -579,258 +590,446 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>about_title_highlight</t>
+          <t>hero_image</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Discipline</t>
+          <t>assets/img/hero-profile.webp</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the About title</t>
+          <t>Photo on the first screen (put the file in assets/img/)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>about_title_rest</t>
+          <t>about_image</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Builds Freedom</t>
+          <t>assets/img/about-profile.webp</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>White part of the About title</t>
+          <t>Photo in the About section</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>about_text</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>I'm a **Cloud &amp; DevOps** engineer in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
+          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Wrap words in **double stars** to make them purple</t>
+          <t>Path or link to your resume PDF (empty = hide the Resume buttons)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>contact_text</t>
+          <t>about_title_highlight</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Open to internships and entry-level Cloud / DevOps roles. Let's talk!</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Line above the Copy email button</t>
+          <t>Purple part of the About title</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>about_title_rest</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>mosaud1997@icloud.com</t>
+          <t>Is My Passion</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact + used by Copy email</t>
+          <t>White part of the About title</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>about_text</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Lucknow, Uttar Pradesh, India</t>
+          <t>I'm a **Cloud &amp; DevOps Engineer** in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact</t>
+          <t>Wrap words in **double stars** to make them purple. Alt+Enter = new line</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>projects_title</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohdsaud1</t>
+          <t>I make Incredible</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Full https:// link</t>
+          <t>White part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>projects_highlight</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Iamsaudkhan</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Full https:// link</t>
+          <t>Purple part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>whatsapp</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr"/>
+          <t>work_title_highlight</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+          <t>Purple part of the Experience title</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>work_title_rest</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Path or link to your resume PDF</t>
+          <t>White part</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>services_title</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>What I</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>White part of the Services title</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>services_highlight</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Offer</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Purple part</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>testimonials_title_highlight</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>What They Say</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Purple part of the Testimonials title</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>testimonials_title_rest</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>About Me</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>White part</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>contact_title</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Contact Me</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Contact title</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>contact_text</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Open to Cloud / DevOps roles. Let's talk!</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Line above the Copy Email button</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>mosaud1997@icloud.com</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Shown in Contact + used by Copy Email</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Lucknow, Uttar Pradesh, India</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Shown in Contact</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohdsaud1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Full link (empty = hidden)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Iamsaudkhan</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Full link (empty = hidden)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>X / Twitter link (empty = hidden)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Empty = hidden</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Empty = hidden</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Empty = hidden</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Empty = hidden</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>telegram</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Example: https://t.me/username</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>messenger</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Example: https://m.me/username</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -1667,7 +1866,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
@@ -1720,7 +1919,8 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Secure Cloud DevSecOps Pipeline</t>
+          <t>Secure Cloud
+DevSecOps Pipeline</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1749,7 +1949,8 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>AWS Infrastructure as Code</t>
+          <t>AWS Infrastructure
+as Code</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1778,12 +1979,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Personal Portfolio Website</t>
+          <t>Portfolio Website</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HTML, CSS, JavaScript, GitHub Pages, Google Sheets</t>
+          <t>HTML, CSS, JavaScript, Swiper JS, Anime JS, GitHub Pages</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3590,9 +3791,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="80" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3647,7 +3848,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sep 2019 – May 2023</t>
+          <t>Sep 2019 -
+May 2023</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3669,7 +3871,8 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>B.Tech, Computer Science</t>
+          <t>B.Tech
+(Computer Science)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3679,7 +3882,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Graduated 2026</t>
+          <t>Graduated
+2026</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3701,7 +3905,8 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect – Associate</t>
+          <t>AWS Solutions
+Architect – Associate</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3733,7 +3938,8 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Diploma, Automobile Engineering</t>
+          <t>Diploma
+(Automobile Engg.)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5376,12 +5582,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cloud &amp; DevOps</t>
+          <t>Cloud &amp; DevOps Skills</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Building, automating and deploying infrastructure on AWS with Infrastructure as Code and CI/CD.</t>
+          <t>Building, automating and deploying infrastructure on AWS with Infrastructure as Code and CI/CD pipelines.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5430,7 +5636,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tools &amp; Languages</t>
+          <t>Development Tools</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -8508,4 +8714,118 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO UPDATE YOUR WEBSITE WITH THIS FILE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1. Edit the text in the tabs Profile, Projects, Experience, Services, Testimonials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2. Save the file (keep the name portfolio-data.xlsx).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3. On GitHub open the repository -&gt; Add file -&gt; Upload files -&gt; drop this file -&gt; Commit changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4. Wait 1-2 minutes and refresh the website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>RULES</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- Do not rename the tabs or the column names in row 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- In the Profile tab only change the 'value' column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- Several items in one cell: separate them with commas (AWS, Terraform, Docker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- New line inside a cell: Alt+Enter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- visible = no hides a row without deleting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- Images: upload the picture to assets/img/ and write assets/img/your-file.png.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- Testimonials: add only real quotes from real people. The section stays hidden while this tab is empty.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -488,488 +488,488 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>greeting</t>
+          <t>page_title</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hello, I'm</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Small purple text above your name</t>
-        </is>
-      </c>
+          <t>Mohd Saud | Cloud &amp; DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>name_line1</t>
+          <t>page_description</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mohd</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Big name, line 1</t>
-        </is>
-      </c>
+          <t>Portfolio of Mohd Saud: Cloud &amp; DevOps engineer in the making, working with AWS, Terraform, Docker, CI/CD and Cloud Security.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>name_line2</t>
+          <t>greeting</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Saud</t>
+          <t>Hello, I'm</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Big name, line 2</t>
+          <t>Small purple text above your name</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>hero_split</t>
+          <t>name_line1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Aspiring</t>
+          <t>Mohd</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Small word above the animated title</t>
+          <t>Big name, line 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>hero_profession1</t>
+          <t>name_line2</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cloud DevOps</t>
+          <t>Saud</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Animated purple line</t>
+          <t>Big name, line 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>hero_profession2</t>
+          <t>hero_split</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Aspiring</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Animated white line</t>
+          <t>Small word above the animated title</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>hero_image</t>
+          <t>hero_profession1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>assets/img/hero-profile.webp</t>
+          <t>Cloud DevOps</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Photo on the first screen (put the file in assets/img/)</t>
+          <t>Animated purple line</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>about_image</t>
+          <t>hero_profession2</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>assets/img/about-profile.webp</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Photo in the About section</t>
+          <t>Animated white line</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>hero_image</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
+          <t>assets/img/hero-profile.webp</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Path or link to your resume PDF (empty = hide the Resume buttons)</t>
+          <t>Photo on the first screen (put the file in assets/img/)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>about_title_highlight</t>
+          <t>about_image</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>assets/img/about-profile.webp</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the About title</t>
+          <t>Photo in the About section</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>about_title_rest</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Is My Passion</t>
+          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>White part of the About title</t>
+          <t>Path or link to your resume PDF (empty = hide the Resume buttons)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>about_text</t>
+          <t>about_title_highlight</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>I'm a **Cloud &amp; DevOps Engineer** in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Wrap words in **double stars** to make them purple. Alt+Enter = new line</t>
+          <t>Purple part of the About title</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>projects_title</t>
+          <t>about_title_rest</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>I make Incredible</t>
+          <t>Is My Passion</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>White part of the Projects title</t>
+          <t>White part of the About title</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>projects_highlight</t>
+          <t>about_text</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>I'm a **Cloud &amp; DevOps Engineer** in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Projects title</t>
+          <t>Wrap words in **double stars** to make them purple. Alt+Enter = new line</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>work_title_highlight</t>
+          <t>projects_title</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>I make Incredible</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Experience title</t>
+          <t>White part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>work_title_rest</t>
+          <t>projects_highlight</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>White part</t>
+          <t>Purple part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>services_title</t>
+          <t>work_title_highlight</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>What I</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>White part of the Services title</t>
+          <t>Purple part of the Experience title</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>services_highlight</t>
+          <t>work_title_rest</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Offer</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Purple part</t>
+          <t>White part</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>testimonials_title_highlight</t>
+          <t>services_title</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What They Say</t>
+          <t>What I</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Testimonials title</t>
+          <t>White part of the Services title</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>testimonials_title_rest</t>
+          <t>services_highlight</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>About Me</t>
+          <t>Offer</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>White part</t>
+          <t>Purple part</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>contact_title</t>
+          <t>testimonials_title_highlight</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Contact Me</t>
+          <t>What They Say</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Contact title</t>
+          <t>Purple part of the Testimonials title</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>contact_text</t>
+          <t>testimonials_title_rest</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Open to Cloud / DevOps roles. Let's talk!</t>
+          <t>About Me</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Line above the Copy Email button</t>
+          <t>White part</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>contact_title</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>mosaud1997@icloud.com</t>
+          <t>Contact Me</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact + used by Copy Email</t>
+          <t>Contact title</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>contact_text</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Lucknow, Uttar Pradesh, India</t>
+          <t>Open to Cloud / DevOps roles. Let's talk!</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact</t>
+          <t>Line above the Copy Email button</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohdsaud1</t>
+          <t>mosaud1997@icloud.com</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Full link (empty = hidden)</t>
+          <t>Shown in Contact + used by Copy Email</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Iamsaudkhan</t>
+          <t>Lucknow, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Full link (empty = hidden)</t>
+          <t>Shown in Contact</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohdsaud1</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>X / Twitter link (empty = hidden)</t>
+          <t>Full link (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr"/>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Iamsaudkhan</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Empty = hidden</t>
+          <t>Full link (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>x</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Empty = hidden</t>
+          <t>X / Twitter link (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -982,7 +982,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -995,51 +995,67 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+          <t>Empty = hidden</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>telegram</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Example: https://t.me/username</t>
+          <t>Empty = hidden</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>messenger</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>telegram</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Example: https://t.me/username</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>messenger</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>Example: https://m.me/username</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -3882,7 +3898,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Graduated
+          <t>Class of
 2026</t>
         </is>
       </c>

--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -582,352 +582,352 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>hero_profession1</t>
+          <t>hero_roles</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cloud DevOps</t>
+          <t>Cloud DevOps Engineer, Cloud Engineer, DevSecOps Engineer, Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Animated purple line</t>
+          <t>Roles that change one by one in the hero, separated by commas (last word goes on the white line)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>hero_profession2</t>
+          <t>hero_image</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>assets/img/hero-profile.webp</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Animated white line</t>
+          <t>Photo on the first screen (put the file in assets/img/)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>hero_image</t>
+          <t>about_image</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>assets/img/hero-profile.webp</t>
+          <t>assets/img/about-profile.webp</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Photo on the first screen (put the file in assets/img/)</t>
+          <t>Photo in the About section</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>about_image</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>assets/img/about-profile.webp</t>
+          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Photo in the About section</t>
+          <t>Path or link to your resume PDF (empty = hide the Resume buttons)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>about_title_highlight</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>assets/pdf/Mohd-Saud-Resume.pdf</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Path or link to your resume PDF (empty = hide the Resume buttons)</t>
+          <t>Purple part of the About title</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>about_title_highlight</t>
+          <t>about_title_rest</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>Is My Passion</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the About title</t>
+          <t>White part of the About title</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>about_title_rest</t>
+          <t>about_text</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Is My Passion</t>
+          <t>I'm a **Cloud &amp; DevOps Engineer** in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>White part of the About title</t>
+          <t>Wrap words in **double stars** to make them purple. Alt+Enter = new line</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>about_text</t>
+          <t>projects_title</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>I'm a **Cloud &amp; DevOps Engineer** in the making, with nearly four years of **customer-facing operations** experience. I build and secure infrastructure on **AWS** using Terraform, Docker and CI/CD, and I'm always learning something new.</t>
+          <t>I make Incredible</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wrap words in **double stars** to make them purple. Alt+Enter = new line</t>
+          <t>White part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>projects_title</t>
+          <t>projects_highlight</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>I make Incredible</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>White part of the Projects title</t>
+          <t>Purple part of the Projects title</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>projects_highlight</t>
+          <t>work_title_highlight</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>My Work</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Projects title</t>
+          <t>Purple part of the Experience title</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>work_title_highlight</t>
+          <t>work_title_rest</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>My Work</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Experience title</t>
+          <t>White part</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>work_title_rest</t>
+          <t>services_title</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>What I</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>White part</t>
+          <t>White part of the Services title</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>services_title</t>
+          <t>services_highlight</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>What I</t>
+          <t>Offer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>White part of the Services title</t>
+          <t>Purple part</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>services_highlight</t>
+          <t>testimonials_title_highlight</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Offer</t>
+          <t>What They Say</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Purple part</t>
+          <t>Purple part of the Testimonials title</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>testimonials_title_highlight</t>
+          <t>testimonials_title_rest</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>What They Say</t>
+          <t>About Me</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Purple part of the Testimonials title</t>
+          <t>White part</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>testimonials_title_rest</t>
+          <t>contact_title</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>About Me</t>
+          <t>Contact Me</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>White part</t>
+          <t>Contact title</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>contact_title</t>
+          <t>contact_text</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Contact Me</t>
+          <t>Open to Cloud / DevOps roles. Let's talk!</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Contact title</t>
+          <t>Line above the Copy Email button</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>contact_text</t>
+          <t>email</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Open to Cloud / DevOps roles. Let's talk!</t>
+          <t>mosaud1997@icloud.com</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Line above the Copy Email button</t>
+          <t>Shown in Contact + used by Copy Email</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>mosaud1997@icloud.com</t>
+          <t>Lucknow, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact + used by Copy Email</t>
+          <t>Shown in Contact</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Lucknow, Uttar Pradesh, India</t>
+          <t>https://www.linkedin.com/in/mohdsaud1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact</t>
+          <t>Full link (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>github</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohdsaud1</t>
+          <t>https://github.com/Iamsaudkhan</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -939,37 +939,33 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/Iamsaudkhan</t>
-        </is>
-      </c>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full link (empty = hidden)</t>
+          <t>X / Twitter link (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>X / Twitter link (empty = hidden)</t>
+          <t>Empty = hidden</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr"/>
@@ -982,7 +978,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr"/>
@@ -995,7 +991,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
@@ -1008,54 +1004,46 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Empty = hidden</t>
+          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>telegram</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Example: https://wa.me/91XXXXXXXXXX (empty = hidden)</t>
+          <t>Example: https://t.me/username</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>telegram</t>
+          <t>messenger</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Example: https://t.me/username</t>
+          <t>Example: https://m.me/username</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>messenger</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Example: https://m.me/username</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>

--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer, Cloud Engineer, DevSecOps Engineer, Cloud Security Engineer</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">

--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -582,7 +582,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>hero_roles</t>
+          <t>hero_role</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Roles that change one by one in the hero, separated by commas (last word goes on the white line)</t>
+          <t>Animated role in the hero (last word goes on the white line)</t>
         </is>
       </c>
     </row>

--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Shown in Contact + used by Copy Email</t>
+          <t>Shown in Contact, as the hero mail icon and by Copy Email</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,11 @@
           <t>instagram</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/i__amsaudkhan/</t>
+        </is>
+      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Empty = hidden</t>

--- a/portfolio-data.xlsx
+++ b/portfolio-data.xlsx
@@ -2003,7 +2003,7 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/MOHDSAUD888/Mohd-Saud_Portfolio-Website</t>
+          <t>https://github.com/MOHDSAUD888/Personal_Portfolio</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8743,9 +8743,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -8774,9 +8772,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
